--- a/data/analysis/momentumImproved/mergeTtestResult/tTestReport-201001_201912_p.xlsx
+++ b/data/analysis/momentumImproved/mergeTtestResult/tTestReport-201001_201912_p.xlsx
@@ -43,289 +43,289 @@
     <t>winner - loser</t>
   </si>
   <si>
-    <t>5.03%</t>
-  </si>
-  <si>
-    <t>(2.69)</t>
-  </si>
-  <si>
-    <t>5.48%</t>
-  </si>
-  <si>
-    <t>(2.85)</t>
-  </si>
-  <si>
-    <t>0.46%</t>
-  </si>
-  <si>
-    <t>(0.30)</t>
-  </si>
-  <si>
-    <t>0.03%</t>
-  </si>
-  <si>
-    <t>(0.02)</t>
-  </si>
-  <si>
-    <t>6.65%</t>
-  </si>
-  <si>
-    <t>(3.74)</t>
-  </si>
-  <si>
-    <t>6.62%</t>
-  </si>
-  <si>
-    <t>(7.03)</t>
-  </si>
-  <si>
-    <t>0.33%</t>
-  </si>
-  <si>
-    <t>(0.20)</t>
-  </si>
-  <si>
-    <t>6.61%</t>
-  </si>
-  <si>
-    <t>(3.53)</t>
-  </si>
-  <si>
-    <t>6.28%</t>
-  </si>
-  <si>
-    <t>(5.58)</t>
-  </si>
-  <si>
-    <t>2.19%</t>
-  </si>
-  <si>
-    <t>(1.20)</t>
-  </si>
-  <si>
-    <t>5.29%</t>
-  </si>
-  <si>
-    <t>(2.81)</t>
-  </si>
-  <si>
-    <t>3.10%</t>
-  </si>
-  <si>
-    <t>(2.38)</t>
-  </si>
-  <si>
-    <t>0.10%</t>
-  </si>
-  <si>
-    <t>(0.09)</t>
-  </si>
-  <si>
-    <t>2.02%</t>
-  </si>
-  <si>
-    <t>(2.16)</t>
-  </si>
-  <si>
-    <t>1.93%</t>
-  </si>
-  <si>
-    <t>(2.76)</t>
-  </si>
-  <si>
-    <t>0.13%</t>
-  </si>
-  <si>
-    <t>(0.13)</t>
-  </si>
-  <si>
-    <t>2.46%</t>
-  </si>
-  <si>
-    <t>(2.98)</t>
-  </si>
-  <si>
-    <t>2.33%</t>
-  </si>
-  <si>
-    <t>(3.67)</t>
-  </si>
-  <si>
-    <t>-0.14%</t>
-  </si>
-  <si>
-    <t>(-0.13)</t>
-  </si>
-  <si>
-    <t>2.84%</t>
-  </si>
-  <si>
-    <t>(3.31)</t>
-  </si>
-  <si>
-    <t>2.99%</t>
-  </si>
-  <si>
-    <t>(4.46)</t>
-  </si>
-  <si>
-    <t>-0.29%</t>
-  </si>
-  <si>
-    <t>(-0.27)</t>
-  </si>
-  <si>
-    <t>2.87%</t>
-  </si>
-  <si>
-    <t>(3.26)</t>
-  </si>
-  <si>
-    <t>3.17%</t>
-  </si>
-  <si>
-    <t>(4.50)</t>
-  </si>
-  <si>
-    <t>0.71%</t>
-  </si>
-  <si>
-    <t>(0.52)</t>
-  </si>
-  <si>
-    <t>3.25%</t>
-  </si>
-  <si>
-    <t>(2.57)</t>
-  </si>
-  <si>
-    <t>2.54%</t>
-  </si>
-  <si>
-    <t>(2.93)</t>
-  </si>
-  <si>
-    <t>-0.22%</t>
-  </si>
-  <si>
-    <t>(-0.19)</t>
-  </si>
-  <si>
-    <t>4.65%</t>
-  </si>
-  <si>
-    <t>(3.89)</t>
-  </si>
-  <si>
-    <t>4.88%</t>
-  </si>
-  <si>
-    <t>(7.17)</t>
-  </si>
-  <si>
-    <t>-0.64%</t>
-  </si>
-  <si>
-    <t>(-0.53)</t>
-  </si>
-  <si>
-    <t>5.34%</t>
-  </si>
-  <si>
-    <t>(4.36)</t>
-  </si>
-  <si>
-    <t>5.99%</t>
-  </si>
-  <si>
-    <t>(8.13)</t>
-  </si>
-  <si>
-    <t>-0.41%</t>
-  </si>
-  <si>
-    <t>(-0.31)</t>
-  </si>
-  <si>
-    <t>4.62%</t>
-  </si>
-  <si>
-    <t>(3.83)</t>
-  </si>
-  <si>
-    <t>(6.22)</t>
-  </si>
-  <si>
-    <t>2.17%</t>
-  </si>
-  <si>
-    <t>(1.35)</t>
-  </si>
-  <si>
-    <t>4.10%</t>
-  </si>
-  <si>
-    <t>(2.59)</t>
-  </si>
-  <si>
-    <t>1.92%</t>
-  </si>
-  <si>
-    <t>(1.68)</t>
-  </si>
-  <si>
-    <t>-0.50%</t>
-  </si>
-  <si>
-    <t>(-0.38)</t>
-  </si>
-  <si>
-    <t>6.25%</t>
-  </si>
-  <si>
-    <t>(4.21)</t>
-  </si>
-  <si>
-    <t>6.74%</t>
-  </si>
-  <si>
-    <t>(8.69)</t>
-  </si>
-  <si>
-    <t>-0.53%</t>
-  </si>
-  <si>
-    <t>(-0.37)</t>
-  </si>
-  <si>
-    <t>6.54%</t>
-  </si>
-  <si>
-    <t>(4.27)</t>
-  </si>
-  <si>
-    <t>7.06%</t>
-  </si>
-  <si>
-    <t>(8.09)</t>
-  </si>
-  <si>
-    <t>0.07%</t>
-  </si>
-  <si>
-    <t>(0.04)</t>
-  </si>
-  <si>
-    <t>5.35%</t>
-  </si>
-  <si>
-    <t>(3.52)</t>
-  </si>
-  <si>
-    <t>5.28%</t>
-  </si>
-  <si>
-    <t>(5.34)</t>
+    <t>0.0503</t>
+  </si>
+  <si>
+    <t>2.6859</t>
+  </si>
+  <si>
+    <t>0.0548</t>
+  </si>
+  <si>
+    <t>2.8549</t>
+  </si>
+  <si>
+    <t>0.0046</t>
+  </si>
+  <si>
+    <t>0.2977</t>
+  </si>
+  <si>
+    <t>0.0003</t>
+  </si>
+  <si>
+    <t>0.0195</t>
+  </si>
+  <si>
+    <t>0.0665</t>
+  </si>
+  <si>
+    <t>3.7415</t>
+  </si>
+  <si>
+    <t>0.0662</t>
+  </si>
+  <si>
+    <t>7.0268</t>
+  </si>
+  <si>
+    <t>0.0033</t>
+  </si>
+  <si>
+    <t>0.1978</t>
+  </si>
+  <si>
+    <t>0.0661</t>
+  </si>
+  <si>
+    <t>3.5332</t>
+  </si>
+  <si>
+    <t>0.0628</t>
+  </si>
+  <si>
+    <t>5.5836</t>
+  </si>
+  <si>
+    <t>0.0219</t>
+  </si>
+  <si>
+    <t>1.2035</t>
+  </si>
+  <si>
+    <t>0.0529</t>
+  </si>
+  <si>
+    <t>2.8147</t>
+  </si>
+  <si>
+    <t>0.0310</t>
+  </si>
+  <si>
+    <t>2.3830</t>
+  </si>
+  <si>
+    <t>0.0010</t>
+  </si>
+  <si>
+    <t>0.0866</t>
+  </si>
+  <si>
+    <t>0.0202</t>
+  </si>
+  <si>
+    <t>2.1632</t>
+  </si>
+  <si>
+    <t>0.0193</t>
+  </si>
+  <si>
+    <t>2.7603</t>
+  </si>
+  <si>
+    <t>0.0013</t>
+  </si>
+  <si>
+    <t>0.1277</t>
+  </si>
+  <si>
+    <t>0.0246</t>
+  </si>
+  <si>
+    <t>2.9832</t>
+  </si>
+  <si>
+    <t>0.0233</t>
+  </si>
+  <si>
+    <t>3.6674</t>
+  </si>
+  <si>
+    <t>-0.0014</t>
+  </si>
+  <si>
+    <t>-0.1338</t>
+  </si>
+  <si>
+    <t>0.0284</t>
+  </si>
+  <si>
+    <t>3.3135</t>
+  </si>
+  <si>
+    <t>0.0299</t>
+  </si>
+  <si>
+    <t>4.4636</t>
+  </si>
+  <si>
+    <t>-0.0029</t>
+  </si>
+  <si>
+    <t>-0.2700</t>
+  </si>
+  <si>
+    <t>0.0287</t>
+  </si>
+  <si>
+    <t>3.2567</t>
+  </si>
+  <si>
+    <t>0.0317</t>
+  </si>
+  <si>
+    <t>4.5005</t>
+  </si>
+  <si>
+    <t>0.0071</t>
+  </si>
+  <si>
+    <t>0.5170</t>
+  </si>
+  <si>
+    <t>0.0325</t>
+  </si>
+  <si>
+    <t>2.5713</t>
+  </si>
+  <si>
+    <t>0.0254</t>
+  </si>
+  <si>
+    <t>2.9274</t>
+  </si>
+  <si>
+    <t>-0.0022</t>
+  </si>
+  <si>
+    <t>-0.1925</t>
+  </si>
+  <si>
+    <t>0.0465</t>
+  </si>
+  <si>
+    <t>3.8905</t>
+  </si>
+  <si>
+    <t>0.0488</t>
+  </si>
+  <si>
+    <t>7.1728</t>
+  </si>
+  <si>
+    <t>-0.0064</t>
+  </si>
+  <si>
+    <t>-0.5250</t>
+  </si>
+  <si>
+    <t>0.0534</t>
+  </si>
+  <si>
+    <t>4.3571</t>
+  </si>
+  <si>
+    <t>0.0599</t>
+  </si>
+  <si>
+    <t>8.1322</t>
+  </si>
+  <si>
+    <t>-0.0041</t>
+  </si>
+  <si>
+    <t>-0.3114</t>
+  </si>
+  <si>
+    <t>0.0462</t>
+  </si>
+  <si>
+    <t>3.8298</t>
+  </si>
+  <si>
+    <t>6.2243</t>
+  </si>
+  <si>
+    <t>0.0217</t>
+  </si>
+  <si>
+    <t>1.3542</t>
+  </si>
+  <si>
+    <t>0.0410</t>
+  </si>
+  <si>
+    <t>2.5897</t>
+  </si>
+  <si>
+    <t>0.0192</t>
+  </si>
+  <si>
+    <t>1.6753</t>
+  </si>
+  <si>
+    <t>-0.0050</t>
+  </si>
+  <si>
+    <t>-0.3811</t>
+  </si>
+  <si>
+    <t>0.0625</t>
+  </si>
+  <si>
+    <t>4.2088</t>
+  </si>
+  <si>
+    <t>0.0674</t>
+  </si>
+  <si>
+    <t>8.6906</t>
+  </si>
+  <si>
+    <t>-0.0053</t>
+  </si>
+  <si>
+    <t>-0.3721</t>
+  </si>
+  <si>
+    <t>0.0654</t>
+  </si>
+  <si>
+    <t>4.2686</t>
+  </si>
+  <si>
+    <t>0.0706</t>
+  </si>
+  <si>
+    <t>8.0859</t>
+  </si>
+  <si>
+    <t>0.0007</t>
+  </si>
+  <si>
+    <t>0.0446</t>
+  </si>
+  <si>
+    <t>0.0535</t>
+  </si>
+  <si>
+    <t>3.5236</t>
+  </si>
+  <si>
+    <t>0.0528</t>
+  </si>
+  <si>
+    <t>5.3448</t>
   </si>
 </sst>
 </file>
